--- a/demo/output_statistics/liteAV 12.6（2.0）_bug统计报表.xlsx
+++ b/demo/output_statistics/liteAV 12.6（2.0）_bug统计报表.xlsx
@@ -161,19 +161,19 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>liteAV 12.6（2.0）_2025-06-17 10:41:26_bug统计报表</t>
+          <t>liteAV 12.6（2.0）_2025-06-27 16:27:53_bug统计报表</t>
         </is>
       </c>
     </row>
@@ -671,136 +671,138 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>测试工具包</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>3</v>
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" s="14" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="N4" s="14" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>1</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="10" t="inlineStr"/>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>测试工具包</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr"/>
-      <c r="H5" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="16" t="n">
-        <v>10</v>
+      <c r="L5" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="E6" s="10" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="15" t="inlineStr"/>
+      <c r="G6" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="H6" s="10" t="n">
         <v>8</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="13" t="n">
         <v>11</v>
       </c>
+      <c r="J6" s="12" t="n">
+        <v>19</v>
+      </c>
       <c r="K6" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>11</v>
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N6" s="13" t="inlineStr">
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -813,38 +815,38 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>28</v>
+      <c r="D7" s="15" t="n">
+        <v>29</v>
       </c>
       <c r="E7" s="10" t="inlineStr"/>
       <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="15" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr"/>
       <c r="H7" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="J7" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L7" s="16" t="n">
+      <c r="J7" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N7" s="13" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -853,134 +855,134 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>插件</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>3</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
       <c r="H8" s="10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>1</v>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>vodplayer</t>
+          <t>插件</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="15" t="inlineStr"/>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="H9" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J9" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>19</v>
+      <c r="K9" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>80%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>TRTCPipeline</t>
+          <t>vodplayer</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr"/>
       <c r="D10" s="10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E10" s="10" t="inlineStr"/>
       <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="15" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr"/>
       <c r="H10" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>21</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -989,42 +991,42 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>自动化环境问题</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr"/>
+          <t>TRTCPipeline</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>10</v>
+      </c>
       <c r="C11" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>2</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr"/>
       <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr"/>
+      <c r="H11" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="I11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>12</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1033,40 +1035,42 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>UGC</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
+          <t>自动化环境问题</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr"/>
+      <c r="C12" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="D12" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="15" t="inlineStr"/>
-      <c r="H12" s="10" t="n">
-        <v>2</v>
-      </c>
+      <c r="G12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr"/>
       <c r="I12" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="K12" s="10" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N12" s="13" t="inlineStr">
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1075,126 +1079,126 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>TRTCNetwork</t>
+          <t>UGC</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>2</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr"/>
       <c r="H13" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>50%</t>
+        <v>7</v>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>美颜</t>
+          <t>TRTCNetwork</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="10" t="inlineStr"/>
+      <c r="C14" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="D14" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="15" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="H14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="13" t="n">
-        <v>1</v>
+      <c r="I14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="K14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="13" t="inlineStr">
+      <c r="L14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>美颜</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="16" t="n">
-        <v>24</v>
+      <c r="D15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="15" t="inlineStr"/>
+      <c r="G15" s="16" t="inlineStr"/>
       <c r="H15" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N15" s="13" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="10" t="inlineStr"/>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1203,40 +1207,40 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>2</v>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="11" t="n">
+        <v>24</v>
       </c>
       <c r="E16" s="10" t="inlineStr"/>
       <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="15" t="inlineStr"/>
+      <c r="G16" s="16" t="inlineStr"/>
       <c r="H16" s="10" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N16" s="13" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1245,36 +1249,40 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>后台</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="D17" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="10" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="15" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
       <c r="H17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="13" t="n">
-        <v>1</v>
+      <c r="I17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="K17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N17" s="13" t="inlineStr">
+      <c r="L17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1283,36 +1291,36 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>LiveKit</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="10" t="n">
-        <v>3</v>
-      </c>
+          <t>后台</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr"/>
       <c r="D18" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="10" t="inlineStr"/>
       <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="15" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" s="10" t="inlineStr"/>
-      <c r="L18" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N18" s="13" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr"/>
+      <c r="H18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="10" t="inlineStr"/>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1321,36 +1329,36 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>TUIRoomKit</t>
+          <t>LiveKit</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="10" t="inlineStr"/>
       <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="15" t="inlineStr"/>
+      <c r="G19" s="16" t="inlineStr"/>
       <c r="H19" s="10" t="inlineStr"/>
       <c r="I19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>3</v>
       </c>
       <c r="K19" s="10" t="inlineStr"/>
       <c r="L19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N19" s="13" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1359,7 +1367,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>TUICallKit</t>
+          <t>TUIRoomKit</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr"/>
@@ -1371,76 +1379,114 @@
       </c>
       <c r="E20" s="10" t="inlineStr"/>
       <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="15" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
       <c r="H20" s="10" t="inlineStr"/>
       <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="13" t="n">
+      <c r="J20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="10" t="inlineStr"/>
       <c r="L20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="13" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N20" s="13" t="inlineStr">
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>TUICallKit</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr"/>
+      <c r="C21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
-        <v>131</v>
-      </c>
-      <c r="C21" s="17" t="n">
+      <c r="B22" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="C22" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D21" s="17" t="n">
-        <v>181</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>92</v>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>80</v>
-      </c>
-      <c r="J21" s="17" t="n">
-        <v>172</v>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v>97</v>
-      </c>
-      <c r="L21" s="17" t="n">
-        <v>84</v>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>95%</t>
+      <c r="D22" s="17" t="n">
+        <v>188</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>178</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
     </row>
